--- a/test/system/data_source/test_cases/objects.xlsx
+++ b/test/system/data_source/test_cases/objects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/em29/git/tol-sdk/test/system/data_source/test_cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78AA916-C6BF-0D42-A274-51B15C4480FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E1A8BB-CA5B-994B-BB1F-75379F67D65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19260" yWindow="680" windowWidth="18980" windowHeight="18900" xr2:uid="{B8D324C6-415D-3B40-B0F4-01C95B855C67}"/>
   </bookViews>
@@ -41,9 +41,6 @@
     <t>sexual_system_in</t>
   </si>
   <si>
-    <t>include_only_strings</t>
-  </si>
-  <si>
     <t>X:-:map_from</t>
   </si>
   <si>
@@ -51,6 +48,9 @@
   </si>
   <si>
     <t>hello-_-world-_-42-_-47584.83</t>
+  </si>
+  <si>
+    <t>include_only_ints</t>
   </si>
 </sst>
 </file>
@@ -436,21 +436,21 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" s="1"/>
     </row>
